--- a/data/trans_dic/P05A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P05A_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,1; 33,15</t>
+          <t>25,02; 33,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,88; 40,51</t>
+          <t>31,45; 40,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,79; 39,81</t>
+          <t>30,58; 40,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,97; 24,57</t>
+          <t>12,39; 24,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,48; 38,05</t>
+          <t>29,25; 37,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,04; 41,67</t>
+          <t>32,07; 41,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,25; 38,55</t>
+          <t>29,38; 38,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,1; 31,97</t>
+          <t>19,05; 31,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,25; 34,38</t>
+          <t>28,35; 34,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,29; 39,44</t>
+          <t>33,13; 39,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,08; 37,79</t>
+          <t>31,5; 37,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,5; 25,59</t>
+          <t>17,38; 26,3</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,52; 31,46</t>
+          <t>24,78; 31,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,77; 43,47</t>
+          <t>36,06; 43,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,05; 40,95</t>
+          <t>32,94; 41,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,4; 22,65</t>
+          <t>14,33; 23,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,19; 35,99</t>
+          <t>28,14; 35,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,86; 42,26</t>
+          <t>34,29; 42,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,59; 42,5</t>
+          <t>34,33; 42,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 22,29</t>
+          <t>16,6; 24,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,18; 32,5</t>
+          <t>27,27; 32,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35,98; 41,67</t>
+          <t>35,83; 41,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,87; 40,27</t>
+          <t>35,03; 40,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,2; 20,69</t>
+          <t>16,55; 22,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,25; 33,93</t>
+          <t>26,14; 33,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,37; 42,33</t>
+          <t>34,51; 42,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,57; 36,65</t>
+          <t>29,65; 37,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 24,89</t>
+          <t>17,68; 24,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,96; 41,38</t>
+          <t>33,97; 41,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,73; 44,14</t>
+          <t>36,87; 44,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,04; 41,17</t>
+          <t>33,61; 41,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,31; 21,16</t>
+          <t>17,97; 23,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,33; 36,73</t>
+          <t>31,43; 36,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,88; 41,95</t>
+          <t>36,78; 42,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,86; 38,38</t>
+          <t>32,62; 38,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 22,09</t>
+          <t>18,85; 23,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,62; 37,5</t>
+          <t>28,25; 36,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 44,13</t>
+          <t>36,06; 44,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,03; 43,2</t>
+          <t>34,87; 42,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 22,84</t>
+          <t>17,76; 24,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,6; 39,88</t>
+          <t>31,63; 39,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,62; 47,65</t>
+          <t>39,68; 48,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,14; 44,17</t>
+          <t>35,61; 43,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 22,99</t>
+          <t>19,37; 24,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,09; 37,45</t>
+          <t>31,3; 37,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38,98; 45,18</t>
+          <t>38,99; 45,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,4; 42,03</t>
+          <t>36,61; 41,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,21; 21,89</t>
+          <t>19,14; 23,04</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,22; 34,68</t>
+          <t>25,93; 34,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,58; 48,63</t>
+          <t>38,87; 48,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,42; 41,68</t>
+          <t>32,13; 41,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,9; 19,63</t>
+          <t>13,63; 19,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,69; 41,5</t>
+          <t>31,33; 41,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,36; 44,05</t>
+          <t>34,45; 44,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,29; 41,44</t>
+          <t>33,03; 41,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,58; 23,67</t>
+          <t>18,66; 24,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,2; 36,86</t>
+          <t>30,15; 36,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37,96; 45,0</t>
+          <t>37,77; 44,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,83; 40,18</t>
+          <t>33,74; 40,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,78; 20,55</t>
+          <t>16,87; 20,63</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,02; 32,65</t>
+          <t>22,8; 32,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,26; 49,43</t>
+          <t>38,0; 50,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,32; 43,98</t>
+          <t>33,12; 43,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,57; 20,88</t>
+          <t>14,86; 21,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,14; 38,87</t>
+          <t>29,08; 38,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,82; 44,92</t>
+          <t>34,73; 45,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,07; 41,64</t>
+          <t>31,82; 42,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,36; 74,83</t>
+          <t>15,47; 21,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,96; 34,77</t>
+          <t>27,83; 34,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38,03; 46,21</t>
+          <t>37,79; 45,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33,55; 41,16</t>
+          <t>33,5; 41,21</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,77; 65,0</t>
+          <t>15,93; 20,02</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,4; 34,86</t>
+          <t>22,79; 34,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,02; 44,41</t>
+          <t>30,48; 43,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,58; 34,6</t>
+          <t>24,31; 35,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,09; 17,89</t>
+          <t>11,29; 18,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,03; 35,21</t>
+          <t>24,63; 34,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,01; 44,17</t>
+          <t>33,59; 44,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,73; 35,45</t>
+          <t>24,62; 35,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,34; 18,38</t>
+          <t>13,45; 18,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24,84; 32,79</t>
+          <t>25,06; 33,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34,24; 42,08</t>
+          <t>34,22; 42,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,86; 33,7</t>
+          <t>25,95; 33,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,27; 17,3</t>
+          <t>13,53; 17,64</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,05; 31,38</t>
+          <t>28,09; 31,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38,02; 41,34</t>
+          <t>37,95; 41,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34,35; 37,62</t>
+          <t>34,32; 37,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,13</t>
+          <t>17,07; 19,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,78; 36,09</t>
+          <t>32,88; 36,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,27; 41,63</t>
+          <t>38,26; 41,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,87; 38,24</t>
+          <t>34,91; 38,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,74; 38,91</t>
+          <t>19,33; 21,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,91; 33,3</t>
+          <t>30,77; 33,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38,58; 41,1</t>
+          <t>38,48; 40,98</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35,17; 37,43</t>
+          <t>35,15; 37,43</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,58; 28,84</t>
+          <t>18,6; 20,44</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70154</t>
+          <t>73962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78095</t>
+          <t>90413</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>148248</t>
+          <t>164374</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>124004; 163784</t>
+          <t>123629; 166366</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>144472; 183598</t>
+          <t>142546; 183817</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129153; 166985</t>
+          <t>128269; 168086</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47859; 98274</t>
+          <t>50514; 100699</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>137795; 177895</t>
+          <t>136721; 174116</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>137537; 178860</t>
+          <t>137641; 179000</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>115777; 152562</t>
+          <t>116282; 153212</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59806; 100130</t>
+          <t>69060; 115847</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>271617; 330576</t>
+          <t>272599; 331328</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>293742; 348015</t>
+          <t>292307; 349533</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>253371; 308038</t>
+          <t>256765; 307032</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>117696; 182505</t>
+          <t>133907; 202556</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74094</t>
+          <t>87878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90479</t>
+          <t>101719</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>164573</t>
+          <t>189598</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>180309; 231407</t>
+          <t>182245; 233342</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>245197; 298012</t>
+          <t>247188; 299609</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>195145; 241790</t>
+          <t>194486; 242220</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56772; 95926</t>
+          <t>68338; 111854</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>176357; 225109</t>
+          <t>176001; 224401</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>206655; 257886</t>
+          <t>209236; 258035</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>194928; 239493</t>
+          <t>193467; 239680</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57630; 114121</t>
+          <t>83264; 121724</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>369959; 442277</t>
+          <t>371131; 438471</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>466270; 540022</t>
+          <t>464342; 539696</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>402427; 464730</t>
+          <t>404252; 466963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>123462; 193608</t>
+          <t>161980; 222213</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113343</t>
+          <t>130626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>107179</t>
+          <t>128500</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>220522</t>
+          <t>259126</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>167670; 216690</t>
+          <t>166977; 213493</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>234140; 288327</t>
+          <t>235071; 288696</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>197825; 245231</t>
+          <t>198399; 248142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93387; 133407</t>
+          <t>109343; 152974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>234257; 285402</t>
+          <t>234303; 289119</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>260499; 313021</t>
+          <t>261475; 314280</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>225128; 272325</t>
+          <t>222296; 273157</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>78698; 125132</t>
+          <t>111849; 146083</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>416176; 487985</t>
+          <t>417454; 486749</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>512690; 583180</t>
+          <t>511309; 583904</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>437257; 510661</t>
+          <t>434026; 506546</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>186592; 249026</t>
+          <t>233944; 287025</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139403</t>
+          <t>146618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>144886</t>
+          <t>158601</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>284290</t>
+          <t>305219</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>148578; 194666</t>
+          <t>146639; 188885</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>219736; 270753</t>
+          <t>221252; 273684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>225846; 278566</t>
+          <t>224863; 276436</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59509; 202778</t>
+          <t>124450; 170917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>162958; 205616</t>
+          <t>163110; 205237</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>243692; 293122</t>
+          <t>244070; 295925</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>234547; 286674</t>
+          <t>231105; 283358</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>120933; 163870</t>
+          <t>142716; 176961</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>321730; 387490</t>
+          <t>323865; 385099</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>478954; 555146</t>
+          <t>479069; 553336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>471024; 543814</t>
+          <t>473725; 543281</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>179368; 350399</t>
+          <t>275180; 331200</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91966</t>
+          <t>98454</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>114233</t>
+          <t>128716</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>206199</t>
+          <t>227171</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>101403; 134111</t>
+          <t>100256; 134965</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>165689; 208813</t>
+          <t>166904; 210221</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154922; 199212</t>
+          <t>153566; 199083</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78027; 110158</t>
+          <t>83077; 116371</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>128032; 167644</t>
+          <t>126573; 168176</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>153165; 196346</t>
+          <t>153572; 196799</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>160455; 205883</t>
+          <t>164094; 208069</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>101686; 129533</t>
+          <t>113466; 147663</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>238827; 291479</t>
+          <t>238430; 291938</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>332215; 393832</t>
+          <t>330520; 393571</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>329748; 391641</t>
+          <t>328842; 395009</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>185964; 227845</t>
+          <t>205448; 251232</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64635</t>
+          <t>72360</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>273695</t>
+          <t>79012</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>338330</t>
+          <t>151371</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>67342; 95522</t>
+          <t>66712; 95034</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>118532; 153131</t>
+          <t>117719; 155986</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>111415; 147032</t>
+          <t>110723; 146154</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53624; 76873</t>
+          <t>60481; 86385</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>99939; 133299</t>
+          <t>99708; 133601</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>123256; 159003</t>
+          <t>122937; 161558</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>117030; 156878</t>
+          <t>119874; 159419</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>99548; 455235</t>
+          <t>67941; 93353</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>177712; 220977</t>
+          <t>176834; 220743</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>252422; 306714</t>
+          <t>250846; 304441</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>238564; 292656</t>
+          <t>238181; 293025</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>163723; 634721</t>
+          <t>134843; 169379</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>66518</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>107523</t>
+          <t>119441</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>47022; 73162</t>
+          <t>47833; 72821</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>77143; 110451</t>
+          <t>75807; 108512</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60608; 88925</t>
+          <t>62471; 91156</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31372; 50596</t>
+          <t>35008; 56968</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>80248; 117577</t>
+          <t>82226; 115983</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>132283; 171821</t>
+          <t>130671; 172050</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98647; 141392</t>
+          <t>98215; 140252</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>56797; 78249</t>
+          <t>62472; 86861</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>135091; 178325</t>
+          <t>136282; 181126</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>218313; 268316</t>
+          <t>218181; 270811</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>169615; 221013</t>
+          <t>170184; 218476</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94026; 122592</t>
+          <t>104807; 136694</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>594599</t>
+          <t>654993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>875086</t>
+          <t>761307</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1469685</t>
+          <t>1416300</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>919208; 1028197</t>
+          <t>920308; 1021510</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1300708; 1414412</t>
+          <t>1298317; 1417843</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1165437; 1276521</t>
+          <t>1164617; 1275558</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>466842; 661663</t>
+          <t>602590; 704913</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1107855; 1219558</t>
+          <t>1111094; 1220849</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1359477; 1478927</t>
+          <t>1359339; 1479418</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1235034; 1354433</t>
+          <t>1236745; 1356620</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>695495; 1443886</t>
+          <t>722211; 810247</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2057115; 2216172</t>
+          <t>2048095; 2207510</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2690560; 2866196</t>
+          <t>2683574; 2858180</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2438907; 2595963</t>
+          <t>2437893; 2595935</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1260212; 2067857</t>
+          <t>1351245; 1485075</t>
         </is>
       </c>
     </row>
